--- a/model_training/Model Results.xlsx
+++ b/model_training/Model Results.xlsx
@@ -1,26 +1,211 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub Repository\Patient_Feedback\model_training\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E38E5E-5138-40D2-B868-068F256054A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="45">
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>logistic regression</t>
+  </si>
+  <si>
+    <t>Random Forrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi Head </t>
+  </si>
+  <si>
+    <t>Stacked Model</t>
+  </si>
+  <si>
+    <t>BERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 macro </t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>All the numbers on the right, in the block are wrong, for they have used text 1 to classify features for text 2</t>
+  </si>
+  <si>
+    <t>Single Head</t>
+  </si>
+  <si>
+    <t>Out of Scope</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>domain (3)</t>
+  </si>
+  <si>
+    <t>category (7)</t>
+  </si>
+  <si>
+    <t>subcategory (27)</t>
+  </si>
+  <si>
+    <t>severity_level (4)</t>
+  </si>
+  <si>
+    <t>classification_ar (78)</t>
+  </si>
+  <si>
+    <t>stage (6)</t>
+  </si>
+  <si>
+    <t>harm_level (6)</t>
+  </si>
+  <si>
+    <t>Training Models Stage:  Single Head vs Multi Head</t>
+  </si>
+  <si>
+    <t>Training Models Stage:  Text 23 , Text 123 , Text 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text 1 </t>
+  </si>
+  <si>
+    <t>Text 23</t>
+  </si>
+  <si>
+    <t>Text 123</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>severity_level (3)</t>
+  </si>
+  <si>
+    <t>(Cardinaly)</t>
+  </si>
+  <si>
+    <t>improvement_opportunity_type (2)</t>
+  </si>
+  <si>
+    <t>Stacked Model with different Order</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Text Source</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Patient text</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Subcategory</t>
+  </si>
+  <si>
+    <t>Patient text (optionally + domain/category)</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Patient + Hospital text</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <r>
+      <t>Hospital text ONLY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ← discovered today</t>
+    </r>
+  </si>
+  <si>
+    <t>Harm level</t>
+  </si>
+  <si>
+    <t>Hospital text + patient text</t>
+  </si>
+  <si>
+    <t>Opportunity type</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Each target feature gets its own stacked model.</t>
+    </r>
+  </si>
+  <si>
+    <t>There is NOT one giant stacked model for all features at once.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +213,69 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,17 +283,227 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -330,10 +778,1175 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:X41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="22.5703125" customWidth="1"/>
+    <col min="23" max="23" width="56.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+    </row>
+    <row r="4" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+    </row>
+    <row r="5" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12">
+        <v>2</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12">
+        <v>3</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12">
+        <v>4</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12">
+        <v>5</v>
+      </c>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12">
+        <v>6</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12">
+        <v>7</v>
+      </c>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12">
+        <v>8</v>
+      </c>
+      <c r="T5" s="12"/>
+    </row>
+    <row r="6" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="22">
+        <v>1</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="22">
+        <v>2</v>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="22">
+        <v>3</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="K7" s="22">
+        <v>4</v>
+      </c>
+      <c r="L7" s="23"/>
+      <c r="M7" s="22">
+        <v>5</v>
+      </c>
+      <c r="N7" s="23"/>
+      <c r="O7" s="22">
+        <v>6</v>
+      </c>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="22">
+        <v>7</v>
+      </c>
+      <c r="R7" s="23"/>
+      <c r="S7" s="22">
+        <v>8</v>
+      </c>
+      <c r="T7" s="23"/>
+    </row>
+    <row r="8" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="2"/>
+      <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="16"/>
+      <c r="M8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="16"/>
+      <c r="O8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="16"/>
+      <c r="S8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="T8" s="16"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+    </row>
+    <row r="9" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.72243100000000005</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.44762400000000002</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.60215099999999999</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.21970899999999999</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.45161299999999999</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.15160000000000001</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0.31180000000000002</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0.314</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.6774</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0.394374</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0.52222199999999996</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0.23370199999999999</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0.45054899999999998</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0.69152499999999995</v>
+      </c>
+      <c r="T10" s="6">
+        <v>0.96703300000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="13"/>
+      <c r="D11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.53239800000000004</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.73118300000000003</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.24074499999999999</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.56989199999999995</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.173648</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.44085999999999997</v>
+      </c>
+      <c r="K11" s="6">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0.2581</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.79569999999999996</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0.188828</v>
+      </c>
+      <c r="P11" s="6">
+        <v>0.44444400000000001</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0.216111</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0.38461499999999998</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0.49723800000000001</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0.98901099999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.72243100000000005</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.44762400000000002</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.60215099999999999</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="6">
+        <v>0.15159700000000001</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0.31182799999999999</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+    </row>
+    <row r="13" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.48483100000000001</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.48483100000000001</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.634409</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.123589</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0.30107499999999998</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+    </row>
+    <row r="14" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.26850000000000002</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.67420000000000002</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.1007</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.44940000000000002</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.17979999999999999</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1.06E-2</v>
+      </c>
+      <c r="L14" s="6">
+        <v>7.8700000000000006E-2</v>
+      </c>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+    </row>
+    <row r="15" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="9"/>
+      <c r="M16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+    </row>
+    <row r="17" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+    </row>
+    <row r="18" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+    </row>
+    <row r="20" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+    </row>
+    <row r="21" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="17"/>
+      <c r="C22" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+    </row>
+    <row r="23" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="17"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+    </row>
+    <row r="24" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+    </row>
+    <row r="25" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="22">
+        <v>1</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="G25" s="22">
+        <v>2</v>
+      </c>
+      <c r="H25" s="23"/>
+      <c r="I25" s="22">
+        <v>3</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="K25" s="22">
+        <v>4</v>
+      </c>
+      <c r="L25" s="23"/>
+      <c r="M25" s="22">
+        <v>5</v>
+      </c>
+      <c r="N25" s="23"/>
+      <c r="O25" s="22">
+        <v>6</v>
+      </c>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="22">
+        <v>7</v>
+      </c>
+      <c r="R25" s="23"/>
+      <c r="S25" s="22">
+        <v>8</v>
+      </c>
+      <c r="T25" s="23"/>
+      <c r="V25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="W25" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="16"/>
+      <c r="K26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="16"/>
+      <c r="M26" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="16"/>
+      <c r="O26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="R26" s="16"/>
+      <c r="S26" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="T26" s="16"/>
+      <c r="V26" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="W26" s="25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V27" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="W27" s="25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.72243100000000005</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0.44762400000000002</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0.60215099999999999</v>
+      </c>
+      <c r="I28" s="6">
+        <v>0.19802600000000001</v>
+      </c>
+      <c r="J28" s="6">
+        <v>0.44085999999999997</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0.15159700000000001</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0.31182799999999999</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O28" s="6">
+        <v>0.38979999999999998</v>
+      </c>
+      <c r="P28" s="6">
+        <v>0.56669999999999998</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.23369999999999999</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="S28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="V28" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="W28" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.53239800000000004</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.73118300000000003</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0.42820000000000003</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="I29" s="6">
+        <v>0.13500499999999999</v>
+      </c>
+      <c r="J29" s="6">
+        <v>0.37634400000000001</v>
+      </c>
+      <c r="K29" s="6">
+        <v>8.3047999999999997E-2</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0.25806499999999999</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0.314</v>
+      </c>
+      <c r="N29" s="20">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="O29" s="6">
+        <v>0.45989999999999998</v>
+      </c>
+      <c r="P29" s="6">
+        <v>0.57779999999999998</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0.22359999999999999</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0.37359999999999999</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="V29" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="W29" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="5"/>
+      <c r="D30" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.72243100000000005</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0.27850000000000003</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.52690000000000003</v>
+      </c>
+      <c r="I30" s="6"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="6">
+        <v>0.15159700000000001</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0.31182799999999999</v>
+      </c>
+      <c r="M30" s="6">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="N30" s="6">
+        <v>0.79569999999999996</v>
+      </c>
+      <c r="O30" s="6">
+        <v>0.25790000000000002</v>
+      </c>
+      <c r="P30" s="6">
+        <v>0.5111</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0.22689999999999999</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0.3846</v>
+      </c>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="V30" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="W30" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="20">
+        <v>0.48483100000000001</v>
+      </c>
+      <c r="F31" s="20">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G31" s="20">
+        <v>0.4128</v>
+      </c>
+      <c r="H31" s="20">
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="I31" s="20">
+        <v>0.123589</v>
+      </c>
+      <c r="J31" s="20">
+        <v>0.30107499999999998</v>
+      </c>
+      <c r="K31" s="20"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="20">
+        <v>0.3962</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0.7419</v>
+      </c>
+      <c r="O31" s="20">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="P31" s="20">
+        <v>0.57779999999999998</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0.47249999999999998</v>
+      </c>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="V31" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="W31" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="20">
+        <v>0.48483100000000001</v>
+      </c>
+      <c r="F32" s="20">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G32" s="20">
+        <v>0.2797</v>
+      </c>
+      <c r="H32" s="20">
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="I32" s="20">
+        <v>0.123589</v>
+      </c>
+      <c r="J32" s="20">
+        <v>0.30107499999999998</v>
+      </c>
+      <c r="K32" s="20"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="20">
+        <v>0.40079999999999999</v>
+      </c>
+      <c r="N32" s="20">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="O32" s="20">
+        <v>0.25180000000000002</v>
+      </c>
+      <c r="P32" s="20">
+        <v>0.4889</v>
+      </c>
+      <c r="Q32" s="20">
+        <v>0.247</v>
+      </c>
+      <c r="R32" s="20">
+        <v>0.41760000000000003</v>
+      </c>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="V32" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="W32" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+    </row>
+    <row r="34" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W35" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+    </row>
+    <row r="38" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+    </row>
+    <row r="39" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="C37:T38"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="C22:T23"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="C3:T4"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="M16:T17"/>
+    <mergeCell ref="O19:S20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S8:T8"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E10:T14">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>E10&lt;0.6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="10">
+      <formula>AND(E10&gt;=0.6,E10&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>AND(E10&gt;=0.7,E10&lt;0.8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="12">
+      <formula>E10&gt;=0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:T31">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>E28&lt;0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>AND(E28&gt;=0.55,E28&lt;0.65)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>AND(E28&gt;=65,E28&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>E28&gt;=0.7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32:T32">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>E32&lt;0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>AND(E32&gt;=0.55,E32&lt;0.65)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>AND(E32&gt;=65,E32&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>E32&gt;=0.7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/model_training/Model Results.xlsx
+++ b/model_training/Model Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub Repository\Patient_Feedback\model_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E38E5E-5138-40D2-B868-068F256054A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94ED2CA8-3C10-4006-9706-7C1631FEFC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="65">
   <si>
     <t>Accuracy</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Subcategory</t>
   </si>
   <si>
-    <t>Patient text (optionally + domain/category)</t>
-  </si>
-  <si>
     <t>Severity</t>
   </si>
   <si>
@@ -153,21 +150,6 @@
   </si>
   <si>
     <t>Stage</t>
-  </si>
-  <si>
-    <r>
-      <t>Hospital text ONLY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ← discovered today</t>
-    </r>
   </si>
   <si>
     <t>Harm level</t>
@@ -197,6 +179,84 @@
   <si>
     <t>There is NOT one giant stacked model for all features at once.</t>
   </si>
+  <si>
+    <t xml:space="preserve">Patient text </t>
+  </si>
+  <si>
+    <r>
+      <t>Hospital text ONLY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Hierarchial Model</t>
+  </si>
+  <si>
+    <t>MPNET</t>
+  </si>
+  <si>
+    <t>category - 1 (7)</t>
+  </si>
+  <si>
+    <t>category - 2 (7)</t>
+  </si>
+  <si>
+    <t>category - 3 (7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SubCategory - 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SubCategory - 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SubCategory - 3 </t>
+  </si>
+  <si>
+    <t>SubCategory - 4</t>
+  </si>
+  <si>
+    <t>SubCategory - 6</t>
+  </si>
+  <si>
+    <t>SubCategory - 5</t>
+  </si>
+  <si>
+    <t>SubCategory - 7</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>Seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPNET </t>
+  </si>
+  <si>
+    <t>logistic regression (Weight)</t>
+  </si>
+  <si>
+    <t>Random Forrest (Weight)</t>
+  </si>
+  <si>
+    <t>XGBoost (Weight)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hierarchial </t>
+  </si>
+  <si>
+    <t>Key Phrases Usage</t>
+  </si>
 </sst>
 </file>
 
@@ -205,7 +265,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +320,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -275,7 +350,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -337,17 +412,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -365,33 +448,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,23 +461,62 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -472,6 +570,62 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -779,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:X41"/>
+  <dimension ref="B2:Z56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -793,80 +947,80 @@
   <sheetData>
     <row r="2" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
     </row>
     <row r="4" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
     </row>
     <row r="5" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E5" s="12">
+      <c r="E5" s="23">
         <v>1</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23">
         <v>2</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12">
+      <c r="H5" s="23"/>
+      <c r="I5" s="23">
         <v>3</v>
       </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23">
         <v>4</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12">
+      <c r="L5" s="23"/>
+      <c r="M5" s="23">
         <v>5</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12">
-        <v>6</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12">
+      <c r="N5" s="23"/>
+      <c r="O5" s="23">
+        <v>6</v>
+      </c>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23">
         <v>7</v>
       </c>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12">
+      <c r="R5" s="23"/>
+      <c r="S5" s="23">
         <v>8</v>
       </c>
-      <c r="T5" s="12"/>
+      <c r="T5" s="23"/>
     </row>
     <row r="6" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
@@ -876,80 +1030,80 @@
     <row r="7" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="22">
+      <c r="E7" s="19">
         <v>1</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="22">
+      <c r="F7" s="20"/>
+      <c r="G7" s="19">
         <v>2</v>
       </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="22">
+      <c r="H7" s="20"/>
+      <c r="I7" s="19">
         <v>3</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="22">
+      <c r="J7" s="20"/>
+      <c r="K7" s="19">
         <v>4</v>
       </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="22">
+      <c r="L7" s="20"/>
+      <c r="M7" s="19">
         <v>5</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="22">
-        <v>6</v>
-      </c>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="22">
+      <c r="N7" s="20"/>
+      <c r="O7" s="19">
+        <v>6</v>
+      </c>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="19">
         <v>7</v>
       </c>
-      <c r="R7" s="23"/>
-      <c r="S7" s="22">
+      <c r="R7" s="20"/>
+      <c r="S7" s="19">
         <v>8</v>
       </c>
-      <c r="T7" s="23"/>
+      <c r="T7" s="20"/>
     </row>
     <row r="8" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="2"/>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="15" t="s">
+      <c r="F8" s="18"/>
+      <c r="G8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="15" t="s">
+      <c r="H8" s="18"/>
+      <c r="I8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15" t="s">
+      <c r="J8" s="18"/>
+      <c r="K8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="15" t="s">
+      <c r="L8" s="18"/>
+      <c r="M8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="15" t="s">
+      <c r="N8" s="18"/>
+      <c r="O8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="15" t="s">
+      <c r="P8" s="18"/>
+      <c r="Q8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="16"/>
-      <c r="S8" s="15" t="s">
+      <c r="R8" s="18"/>
+      <c r="S8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T8" s="16"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
     </row>
     <row r="9" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="2"/>
@@ -1004,415 +1158,476 @@
       </c>
     </row>
     <row r="10" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0.72243100000000005</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>0.81720400000000004</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>0.44762400000000002</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>0.60215099999999999</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>0.21970899999999999</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>0.45161299999999999</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>0.15160000000000001</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>0.31180000000000002</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>0.314</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>0.6774</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <v>0.394374</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <v>0.52222199999999996</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <v>0.23370199999999999</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="5">
         <v>0.45054899999999998</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="5">
         <v>0.69152499999999995</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="5">
         <v>0.96703300000000003</v>
       </c>
     </row>
     <row r="11" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="13"/>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>0.53239800000000004</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>0.73118300000000003</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>0.24074499999999999</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>0.56989199999999995</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>0.173648</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <v>0.44085999999999997</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>0.2581</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>0.29899999999999999</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <v>0.79569999999999996</v>
       </c>
-      <c r="O11" s="6">
+      <c r="O11" s="5">
         <v>0.188828</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="5">
         <v>0.44444400000000001</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="Q11" s="5">
         <v>0.216111</v>
       </c>
-      <c r="R11" s="6">
+      <c r="R11" s="5">
         <v>0.38461499999999998</v>
       </c>
-      <c r="S11" s="6">
+      <c r="S11" s="5">
         <v>0.49723800000000001</v>
       </c>
-      <c r="T11" s="6">
+      <c r="T11" s="5">
         <v>0.98901099999999997</v>
       </c>
     </row>
     <row r="12" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>0.72243100000000005</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>0.81720400000000004</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>0.44762400000000002</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>0.60215099999999999</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="6">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="5">
         <v>0.15159700000000001</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>0.31182799999999999</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
     </row>
     <row r="13" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="3"/>
-      <c r="D13" s="4" t="s">
+      <c r="C13" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>0.48483100000000001</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>0.81720400000000004</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>0.48483100000000001</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>0.634409</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>0.123589</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <v>0.30107499999999998</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
     </row>
     <row r="14" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="3"/>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>0.26850000000000002</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>0.67420000000000002</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>0.1007</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>0.44940000000000002</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>0.17979999999999999</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>1.06E-2</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>7.8700000000000006E-2</v>
       </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-    </row>
-    <row r="15" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+    </row>
+    <row r="15" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+    </row>
     <row r="16" spans="3:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K16" s="9" t="s">
+      <c r="C16" s="1"/>
+      <c r="D16" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+    </row>
+    <row r="17" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="10" t="s">
+      <c r="L17" s="22"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-    </row>
-    <row r="17" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="27"/>
     </row>
     <row r="18" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
     </row>
     <row r="20" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
     </row>
     <row r="21" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17"/>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
     </row>
     <row r="23" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="17"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
     </row>
     <row r="24" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
     </row>
     <row r="25" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="22">
+      <c r="E25" s="19">
         <v>1</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="22">
+      <c r="F25" s="20"/>
+      <c r="G25" s="19">
         <v>2</v>
       </c>
-      <c r="H25" s="23"/>
-      <c r="I25" s="22">
+      <c r="H25" s="20"/>
+      <c r="I25" s="19">
         <v>3</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="22">
+      <c r="J25" s="20"/>
+      <c r="K25" s="19">
         <v>4</v>
       </c>
-      <c r="L25" s="23"/>
-      <c r="M25" s="22">
+      <c r="L25" s="20"/>
+      <c r="M25" s="19">
         <v>5</v>
       </c>
-      <c r="N25" s="23"/>
-      <c r="O25" s="22">
-        <v>6</v>
-      </c>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="22">
+      <c r="N25" s="20"/>
+      <c r="O25" s="19">
+        <v>6</v>
+      </c>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="19">
         <v>7</v>
       </c>
-      <c r="R25" s="23"/>
-      <c r="S25" s="22">
+      <c r="R25" s="20"/>
+      <c r="S25" s="19">
         <v>8</v>
       </c>
-      <c r="T25" s="23"/>
-      <c r="V25" s="8" t="s">
+      <c r="T25" s="20"/>
+      <c r="V25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="W25" s="8" t="s">
+      <c r="W25" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="15" t="s">
+      <c r="F26" s="18"/>
+      <c r="G26" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="15" t="s">
+      <c r="H26" s="18"/>
+      <c r="I26" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="15" t="s">
+      <c r="J26" s="18"/>
+      <c r="K26" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="L26" s="16"/>
-      <c r="M26" s="15" t="s">
+      <c r="L26" s="18"/>
+      <c r="M26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="N26" s="16"/>
-      <c r="O26" s="15" t="s">
+      <c r="N26" s="18"/>
+      <c r="O26" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="15" t="s">
+      <c r="P26" s="18"/>
+      <c r="Q26" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="16"/>
-      <c r="S26" s="15" t="s">
+      <c r="R26" s="18"/>
+      <c r="S26" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T26" s="16"/>
-      <c r="V26" s="24" t="s">
+      <c r="T26" s="18"/>
+      <c r="V26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="W26" s="25" t="s">
+      <c r="W26" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1467,406 +1682,1006 @@
       <c r="T27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="V27" s="24" t="s">
+      <c r="V27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="W27" s="25" t="s">
+      <c r="W27" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>0.72243100000000005</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="5">
         <v>0.81720400000000004</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>0.44762400000000002</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="5">
         <v>0.60215099999999999</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="5">
         <v>0.19802600000000001</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="5">
         <v>0.44085999999999997</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>0.15159700000000001</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>0.31182799999999999</v>
       </c>
-      <c r="M28" s="6" t="s">
+      <c r="M28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="N28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="5">
         <v>0.38979999999999998</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="5">
         <v>0.56669999999999998</v>
       </c>
-      <c r="Q28" s="6">
+      <c r="Q28" s="5">
         <v>0.23369999999999999</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R28" s="5">
         <v>0.45050000000000001</v>
       </c>
-      <c r="S28" s="6" t="s">
+      <c r="S28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="T28" s="6" t="s">
+      <c r="T28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="V28" s="24" t="s">
+      <c r="V28" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="W28" s="25" t="s">
+      <c r="W28" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.53239800000000004</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0.73118300000000003</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0.42820000000000003</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="I29" s="5">
+        <v>0.13500499999999999</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0.37634400000000001</v>
+      </c>
+      <c r="K29" s="5">
+        <v>8.3047999999999997E-2</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0.25806499999999999</v>
+      </c>
+      <c r="M29" s="5">
+        <v>0.314</v>
+      </c>
+      <c r="N29" s="11">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="O29" s="5">
+        <v>0.45989999999999998</v>
+      </c>
+      <c r="P29" s="5">
+        <v>0.57779999999999998</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>0.22359999999999999</v>
+      </c>
+      <c r="R29" s="5">
+        <v>0.37359999999999999</v>
+      </c>
+      <c r="S29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="V29" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="W29" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="4"/>
+      <c r="D30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.72243100000000005</v>
+      </c>
+      <c r="F30" s="5">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G30" s="5">
+        <v>0.27850000000000003</v>
+      </c>
+      <c r="H30" s="5">
+        <v>0.52690000000000003</v>
+      </c>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="5">
+        <v>0.15159700000000001</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.31182799999999999</v>
+      </c>
+      <c r="M30" s="5">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0.79569999999999996</v>
+      </c>
+      <c r="O30" s="5">
+        <v>0.25790000000000002</v>
+      </c>
+      <c r="P30" s="5">
+        <v>0.5111</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>0.22689999999999999</v>
+      </c>
+      <c r="R30" s="5">
+        <v>0.3846</v>
+      </c>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="V30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="W30" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E29" s="6">
-        <v>0.53239800000000004</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0.73118300000000003</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0.42820000000000003</v>
-      </c>
-      <c r="H29" s="6">
+      <c r="E31" s="11">
+        <v>0.48483100000000001</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0.81720400000000004</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0.4128</v>
+      </c>
+      <c r="H31" s="11">
         <v>0.55910000000000004</v>
       </c>
-      <c r="I29" s="6">
-        <v>0.13500499999999999</v>
-      </c>
-      <c r="J29" s="6">
-        <v>0.37634400000000001</v>
-      </c>
-      <c r="K29" s="6">
-        <v>8.3047999999999997E-2</v>
-      </c>
-      <c r="L29" s="6">
-        <v>0.25806499999999999</v>
-      </c>
-      <c r="M29" s="6">
-        <v>0.314</v>
-      </c>
-      <c r="N29" s="20">
-        <v>0.67700000000000005</v>
-      </c>
-      <c r="O29" s="6">
-        <v>0.45989999999999998</v>
-      </c>
-      <c r="P29" s="6">
+      <c r="I31" s="11">
+        <v>0.123589</v>
+      </c>
+      <c r="J31" s="11">
+        <v>0.30107499999999998</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="11">
+        <v>0.3962</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0.7419</v>
+      </c>
+      <c r="O31" s="11">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="P31" s="11">
         <v>0.57779999999999998</v>
       </c>
-      <c r="Q29" s="6">
-        <v>0.22359999999999999</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0.37359999999999999</v>
-      </c>
-      <c r="S29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="T29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="V29" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="W29" s="25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="5"/>
-      <c r="D30" s="4" t="s">
+      <c r="Q31" s="5">
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="R31" s="5">
+        <v>0.47249999999999998</v>
+      </c>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="V31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="W31" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="6">
-        <v>0.72243100000000005</v>
-      </c>
-      <c r="F30" s="6">
+      <c r="E32" s="11">
+        <v>0.48483100000000001</v>
+      </c>
+      <c r="F32" s="11">
         <v>0.81720400000000004</v>
       </c>
-      <c r="G30" s="6">
-        <v>0.27850000000000003</v>
-      </c>
-      <c r="H30" s="6">
-        <v>0.52690000000000003</v>
-      </c>
-      <c r="I30" s="6"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="6">
-        <v>0.15159700000000001</v>
-      </c>
-      <c r="L30" s="6">
-        <v>0.31182799999999999</v>
-      </c>
-      <c r="M30" s="6">
-        <v>0.29899999999999999</v>
-      </c>
-      <c r="N30" s="6">
-        <v>0.79569999999999996</v>
-      </c>
-      <c r="O30" s="6">
-        <v>0.25790000000000002</v>
-      </c>
-      <c r="P30" s="6">
-        <v>0.5111</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0.22689999999999999</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0.3846</v>
-      </c>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="V30" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="W30" s="25" t="s">
+      <c r="G32" s="11">
+        <v>0.2797</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.123589</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.30107499999999998</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="11">
+        <v>0.40079999999999999</v>
+      </c>
+      <c r="N32" s="11">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="O32" s="11">
+        <v>0.25180000000000002</v>
+      </c>
+      <c r="P32" s="11">
+        <v>0.4889</v>
+      </c>
+      <c r="Q32" s="11">
+        <v>0.247</v>
+      </c>
+      <c r="R32" s="11">
+        <v>0.41760000000000003</v>
+      </c>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="V32" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="W32" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="4" t="s">
+    <row r="33" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+    </row>
+    <row r="34" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="W34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W35" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+    </row>
+    <row r="38" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+    </row>
+    <row r="39" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+    </row>
+    <row r="42" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+    </row>
+    <row r="45" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="19">
         <v>1</v>
       </c>
-      <c r="E31" s="20">
-        <v>0.48483100000000001</v>
-      </c>
-      <c r="F31" s="20">
-        <v>0.81720400000000004</v>
-      </c>
-      <c r="G31" s="20">
-        <v>0.4128</v>
-      </c>
-      <c r="H31" s="20">
-        <v>0.55910000000000004</v>
-      </c>
-      <c r="I31" s="20">
-        <v>0.123589</v>
-      </c>
-      <c r="J31" s="20">
-        <v>0.30107499999999998</v>
-      </c>
-      <c r="K31" s="20"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="20">
-        <v>0.3962</v>
-      </c>
-      <c r="N31" s="20">
-        <v>0.7419</v>
-      </c>
-      <c r="O31" s="20">
-        <v>0.34439999999999998</v>
-      </c>
-      <c r="P31" s="20">
-        <v>0.57779999999999998</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0.24390000000000001</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0.47249999999999998</v>
-      </c>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="V31" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="W31" s="25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="F45" s="20"/>
+      <c r="G45" s="19">
         <v>2</v>
       </c>
-      <c r="E32" s="20">
-        <v>0.48483100000000001</v>
-      </c>
-      <c r="F32" s="20">
-        <v>0.81720400000000004</v>
-      </c>
-      <c r="G32" s="20">
-        <v>0.2797</v>
-      </c>
-      <c r="H32" s="20">
-        <v>0.55910000000000004</v>
-      </c>
-      <c r="I32" s="20">
-        <v>0.123589</v>
-      </c>
-      <c r="J32" s="20">
-        <v>0.30107499999999998</v>
-      </c>
-      <c r="K32" s="20"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="20">
-        <v>0.40079999999999999</v>
-      </c>
-      <c r="N32" s="20">
-        <v>0.82799999999999996</v>
-      </c>
-      <c r="O32" s="20">
-        <v>0.25180000000000002</v>
-      </c>
-      <c r="P32" s="20">
-        <v>0.4889</v>
-      </c>
-      <c r="Q32" s="20">
-        <v>0.247</v>
-      </c>
-      <c r="R32" s="20">
-        <v>0.41760000000000003</v>
-      </c>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="V32" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="W32" s="25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-    </row>
-    <row r="34" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="W34" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W35" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-    </row>
-    <row r="38" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-    </row>
-    <row r="39" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="3:23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="19">
+        <v>3</v>
+      </c>
+      <c r="J45" s="20"/>
+      <c r="K45" s="19">
+        <v>4</v>
+      </c>
+      <c r="L45" s="20"/>
+      <c r="M45" s="19">
+        <v>5</v>
+      </c>
+      <c r="N45" s="20"/>
+      <c r="O45" s="19">
+        <v>6</v>
+      </c>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="19">
+        <v>7</v>
+      </c>
+      <c r="R45" s="20"/>
+      <c r="S45" s="19">
+        <v>8</v>
+      </c>
+      <c r="T45" s="20"/>
+      <c r="U45" s="19">
+        <v>9</v>
+      </c>
+      <c r="V45" s="20"/>
+      <c r="W45" s="19">
+        <v>10</v>
+      </c>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="19">
+        <v>11</v>
+      </c>
+      <c r="Z45" s="20"/>
+    </row>
+    <row r="46" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="18"/>
+      <c r="G46" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="18"/>
+      <c r="I46" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J46" s="18"/>
+      <c r="K46" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="18"/>
+      <c r="M46" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="N46" s="18"/>
+      <c r="O46" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="R46" s="18"/>
+      <c r="S46" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="T46" s="18"/>
+      <c r="U46" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="V46" s="18"/>
+      <c r="W46" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z46" s="18"/>
+    </row>
+    <row r="47" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z47" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="F48" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="G48" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="H48" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="P48" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="R48" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S48" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T48" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="U48" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V48" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="W48" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="X48" s="11">
+        <v>0.36</v>
+      </c>
+      <c r="Y48" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="Z48" s="11">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="J49" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="L49" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="11"/>
+      <c r="V49" s="11"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+    </row>
+    <row r="50" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N50" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="11"/>
+      <c r="V50" s="11"/>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
+    </row>
+    <row r="51" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="F51" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="K51" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="L51" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="M51" s="11">
+        <v>0.49</v>
+      </c>
+      <c r="N51" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="O51" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="P51" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="Q51" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R51" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="S51" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="T51" s="11">
+        <v>0.44</v>
+      </c>
+      <c r="U51" s="11"/>
+      <c r="V51" s="11"/>
+      <c r="W51" s="11"/>
+      <c r="X51" s="11"/>
+      <c r="Y51" s="11"/>
+      <c r="Z51" s="11"/>
+    </row>
+    <row r="52" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0.67</v>
+      </c>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="11"/>
+      <c r="V52" s="11"/>
+      <c r="W52" s="11"/>
+      <c r="X52" s="11"/>
+      <c r="Y52" s="11"/>
+      <c r="Z52" s="11"/>
+    </row>
+    <row r="53" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0.78</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+      <c r="T53" s="11"/>
+      <c r="U53" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="V53" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="W53" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="X53" s="11">
+        <v>0.36</v>
+      </c>
+      <c r="Y53" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="Z53" s="11">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="11"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="11"/>
+      <c r="W54" s="11"/>
+      <c r="X54" s="11"/>
+      <c r="Y54" s="11"/>
+      <c r="Z54" s="11"/>
+    </row>
+    <row r="55" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="11"/>
+      <c r="V55" s="11"/>
+      <c r="W55" s="11"/>
+      <c r="X55" s="11"/>
+      <c r="Y55" s="11"/>
+      <c r="Z55" s="11"/>
+    </row>
+    <row r="56" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0.78</v>
+      </c>
+      <c r="F56" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
+      <c r="T56" s="11"/>
+      <c r="U56" s="11"/>
+      <c r="V56" s="11"/>
+      <c r="W56" s="11"/>
+      <c r="X56" s="11"/>
+      <c r="Y56" s="11"/>
+      <c r="Z56" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="C37:T38"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="C22:T23"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
+  <mergeCells count="72">
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="S46:T46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="C41:T42"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="O45:P45"/>
+    <mergeCell ref="Q45:R45"/>
+    <mergeCell ref="S45:T45"/>
     <mergeCell ref="S5:T5"/>
+    <mergeCell ref="O19:S20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="C3:T4"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G25:H25"/>
@@ -1881,69 +2696,95 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="M16:T17"/>
-    <mergeCell ref="O19:S20"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="C37:T38"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="C22:T23"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="Y46:Z46"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="W45:X45"/>
+    <mergeCell ref="Y45:Z45"/>
   </mergeCells>
-  <conditionalFormatting sqref="E10:T14">
-    <cfRule type="expression" dxfId="11" priority="9">
+  <conditionalFormatting sqref="E10:T15">
+    <cfRule type="expression" dxfId="19" priority="5">
       <formula>E10&lt;0.6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="18" priority="6">
       <formula>AND(E10&gt;=0.6,E10&lt;0.7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="17" priority="7">
       <formula>AND(E10&gt;=0.7,E10&lt;0.8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>E10&gt;=0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:T31">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>E28&lt;0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+  <conditionalFormatting sqref="E28:T32 U53:V53">
+    <cfRule type="expression" dxfId="15" priority="42">
       <formula>AND(E28&gt;=0.55,E28&lt;0.65)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="14" priority="43">
       <formula>AND(E28&gt;=65,E28&lt;0.7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="13" priority="44">
       <formula>E28&gt;=0.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32:T32">
+  <conditionalFormatting sqref="E48:Z56">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>E48&lt;0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="14">
+      <formula>AND(E48&gt;=0.55,E48&lt;0.65)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="15">
+      <formula>AND(E48&gt;=65,E48&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>E48&gt;=0.7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U53:V53 E28:T32">
+    <cfRule type="expression" dxfId="8" priority="41">
+      <formula>E28&lt;0.55</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U56:V56">
+    <cfRule type="expression" dxfId="7" priority="17">
+      <formula>U56&lt;0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="18">
+      <formula>AND(U56&gt;=0.55,U56&lt;0.65)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="19">
+      <formula>AND(U56&gt;=65,U56&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="20">
+      <formula>U56&gt;=0.7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:T16">
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>E32&lt;0.55</formula>
+      <formula>E16&lt;0.6</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>AND(E32&gt;=0.55,E32&lt;0.65)</formula>
+      <formula>AND(E16&gt;=0.6,E16&lt;0.7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AND(E32&gt;=65,E32&lt;0.7)</formula>
+      <formula>AND(E16&gt;=0.7,E16&lt;0.8)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>E32&gt;=0.7</formula>
+      <formula>E16&gt;=0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
